--- a/InputMetadata/electrodes.xlsx
+++ b/InputMetadata/electrodes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nikla\HiwiStuttgart\MUnitQuest_tutorials\InputMetadata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nikla\Documents\HiwiStuttgart\MUnitQuest_tutorials\InputMetadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC4C2F1-3E6C-4F72-A0F5-76AB0CC53583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45CFA332-8B52-439B-B062-EAEB9ACA692F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{6E2ACFE9-4AC4-48A4-B903-324C8DBCA8DF}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="94">
   <si>
     <t>name</t>
   </si>
@@ -103,9 +103,6 @@
     <t>textile</t>
   </si>
   <si>
-    <t>WS2.1</t>
-  </si>
-  <si>
     <t>ring</t>
   </si>
   <si>
@@ -280,15 +277,9 @@
     <t>intraGrid2CoordSys</t>
   </si>
   <si>
-    <t>someSerialNumber</t>
-  </si>
-  <si>
     <t>E025</t>
   </si>
   <si>
-    <t>OTBioelettronica</t>
-  </si>
-  <si>
     <t>group</t>
   </si>
   <si>
@@ -310,12 +301,6 @@
     <t>concentricNeedleLength</t>
   </si>
   <si>
-    <t>electrodeManufacturer</t>
-  </si>
-  <si>
-    <t>electrodeManufacturersModelName</t>
-  </si>
-  <si>
     <t>electrodeType</t>
   </si>
   <si>
@@ -332,6 +317,18 @@
   </si>
   <si>
     <t>grid3CoordSys</t>
+  </si>
+  <si>
+    <t>ElectrodeManufacturer</t>
+  </si>
+  <si>
+    <t>ElectrodeManufacturersModelName</t>
+  </si>
+  <si>
+    <t>manufacturerPlaceholder</t>
+  </si>
+  <si>
+    <t>manufacturerModelNamePlaceholder</t>
   </si>
 </sst>
 </file>
@@ -377,7 +374,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -393,7 +390,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -710,7 +707,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{183029AA-9DBD-4F3D-9FFB-F65D21AB0593}">
   <dimension ref="A1:P49"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
@@ -718,6 +715,7 @@
     <col min="5" max="5" width="24.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.21875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="30.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
@@ -737,42 +735,42 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J1" t="s">
         <v>80</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L1" t="s">
+        <v>82</v>
+      </c>
+      <c r="M1" t="s">
+        <v>83</v>
+      </c>
+      <c r="N1" t="s">
         <v>90</v>
       </c>
-      <c r="H1" t="s">
-        <v>81</v>
-      </c>
-      <c r="I1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J1" t="s">
-        <v>83</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="O1" t="s">
+        <v>91</v>
+      </c>
+      <c r="P1" t="s">
         <v>84</v>
-      </c>
-      <c r="L1" t="s">
-        <v>85</v>
-      </c>
-      <c r="M1" t="s">
-        <v>86</v>
-      </c>
-      <c r="N1" t="s">
-        <v>87</v>
-      </c>
-      <c r="O1" t="s">
-        <v>88</v>
-      </c>
-      <c r="P1" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -784,7 +782,7 @@
         <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F2" t="s">
         <v>6</v>
@@ -811,10 +809,10 @@
         <v>8</v>
       </c>
       <c r="N2" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="O2" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="P2" t="s">
         <v>11</v>
@@ -822,7 +820,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -834,7 +832,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F3" t="s">
         <v>6</v>
@@ -861,10 +859,10 @@
         <v>8</v>
       </c>
       <c r="N3" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="O3" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="P3" t="s">
         <v>11</v>
@@ -872,7 +870,7 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B4">
         <v>20</v>
@@ -884,7 +882,7 @@
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F4" t="s">
         <v>6</v>
@@ -911,10 +909,10 @@
         <v>8</v>
       </c>
       <c r="N4" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="O4" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="P4" t="s">
         <v>11</v>
@@ -922,7 +920,7 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B5">
         <v>30</v>
@@ -934,7 +932,7 @@
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F5" t="s">
         <v>6</v>
@@ -961,10 +959,10 @@
         <v>8</v>
       </c>
       <c r="N5" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="O5" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="P5" t="s">
         <v>11</v>
@@ -972,7 +970,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -984,7 +982,7 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F6" t="s">
         <v>6</v>
@@ -1011,10 +1009,10 @@
         <v>8</v>
       </c>
       <c r="N6" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="O6" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="P6" t="s">
         <v>11</v>
@@ -1022,7 +1020,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B7">
         <v>10</v>
@@ -1034,7 +1032,7 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F7" t="s">
         <v>6</v>
@@ -1061,10 +1059,10 @@
         <v>8</v>
       </c>
       <c r="N7" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="O7" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="P7" t="s">
         <v>11</v>
@@ -1072,7 +1070,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B8">
         <v>20</v>
@@ -1084,7 +1082,7 @@
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F8" t="s">
         <v>6</v>
@@ -1111,10 +1109,10 @@
         <v>8</v>
       </c>
       <c r="N8" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="O8" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="P8" t="s">
         <v>11</v>
@@ -1122,7 +1120,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B9">
         <v>30</v>
@@ -1134,7 +1132,7 @@
         <v>5</v>
       </c>
       <c r="E9" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F9" t="s">
         <v>6</v>
@@ -1161,10 +1159,10 @@
         <v>8</v>
       </c>
       <c r="N9" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="O9" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="P9" t="s">
         <v>11</v>
@@ -1172,7 +1170,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1184,7 +1182,7 @@
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
@@ -1211,10 +1209,10 @@
         <v>8</v>
       </c>
       <c r="N10" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="O10" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="P10" t="s">
         <v>11</v>
@@ -1222,7 +1220,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B11">
         <v>5</v>
@@ -1234,7 +1232,7 @@
         <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
@@ -1261,10 +1259,10 @@
         <v>8</v>
       </c>
       <c r="N11" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="O11" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="P11" t="s">
         <v>11</v>
@@ -1272,7 +1270,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1284,7 +1282,7 @@
         <v>5</v>
       </c>
       <c r="E12" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
@@ -1311,10 +1309,10 @@
         <v>8</v>
       </c>
       <c r="N12" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="O12" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="P12" t="s">
         <v>11</v>
@@ -1322,7 +1320,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B13">
         <v>5</v>
@@ -1334,7 +1332,7 @@
         <v>5</v>
       </c>
       <c r="E13" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
@@ -1361,10 +1359,10 @@
         <v>8</v>
       </c>
       <c r="N13" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="O13" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="P13" t="s">
         <v>11</v>
@@ -1372,7 +1370,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1384,7 +1382,7 @@
         <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
@@ -1411,10 +1409,10 @@
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="O14" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="P14" t="s">
         <v>11</v>
@@ -1422,7 +1420,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B15">
         <v>5</v>
@@ -1434,7 +1432,7 @@
         <v>5</v>
       </c>
       <c r="E15" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F15" t="s">
         <v>12</v>
@@ -1461,10 +1459,10 @@
         <v>8</v>
       </c>
       <c r="N15" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="O15" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="P15" t="s">
         <v>11</v>
@@ -1472,7 +1470,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1484,7 +1482,7 @@
         <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F16" t="s">
         <v>12</v>
@@ -1511,10 +1509,10 @@
         <v>8</v>
       </c>
       <c r="N16" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="O16" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="P16" t="s">
         <v>11</v>
@@ -1522,7 +1520,7 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B17">
         <v>5</v>
@@ -1534,7 +1532,7 @@
         <v>5</v>
       </c>
       <c r="E17" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F17" t="s">
         <v>12</v>
@@ -1561,10 +1559,10 @@
         <v>8</v>
       </c>
       <c r="N17" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="O17" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="P17" t="s">
         <v>11</v>
@@ -1572,7 +1570,7 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1584,10 +1582,10 @@
         <v>5</v>
       </c>
       <c r="E18" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G18" t="s">
         <v>10</v>
@@ -1611,10 +1609,10 @@
         <v>8</v>
       </c>
       <c r="N18" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="O18" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="P18" t="s">
         <v>11</v>
@@ -1622,7 +1620,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1634,10 +1632,10 @@
         <v>5</v>
       </c>
       <c r="E19" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G19" t="s">
         <v>10</v>
@@ -1661,10 +1659,10 @@
         <v>8</v>
       </c>
       <c r="N19" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="O19" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="P19" t="s">
         <v>11</v>
@@ -1672,7 +1670,7 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1684,10 +1682,10 @@
         <v>5</v>
       </c>
       <c r="E20" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G20" t="s">
         <v>10</v>
@@ -1711,10 +1709,10 @@
         <v>8</v>
       </c>
       <c r="N20" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="O20" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="P20" t="s">
         <v>11</v>
@@ -1722,7 +1720,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B21">
         <v>10</v>
@@ -1734,10 +1732,10 @@
         <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G21" t="s">
         <v>10</v>
@@ -1761,10 +1759,10 @@
         <v>8</v>
       </c>
       <c r="N21" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="O21" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="P21" t="s">
         <v>11</v>
@@ -1772,7 +1770,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B22">
         <v>10</v>
@@ -1784,10 +1782,10 @@
         <v>5</v>
       </c>
       <c r="E22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G22" t="s">
         <v>10</v>
@@ -1811,10 +1809,10 @@
         <v>8</v>
       </c>
       <c r="N22" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="O22" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="P22" t="s">
         <v>11</v>
@@ -1822,7 +1820,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B23">
         <v>10</v>
@@ -1834,10 +1832,10 @@
         <v>5</v>
       </c>
       <c r="E23" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G23" t="s">
         <v>10</v>
@@ -1861,10 +1859,10 @@
         <v>8</v>
       </c>
       <c r="N23" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="O23" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="P23" t="s">
         <v>11</v>
@@ -1872,7 +1870,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B24">
         <v>20</v>
@@ -1884,10 +1882,10 @@
         <v>5</v>
       </c>
       <c r="E24" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G24" t="s">
         <v>10</v>
@@ -1911,10 +1909,10 @@
         <v>8</v>
       </c>
       <c r="N24" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="O24" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="P24" t="s">
         <v>11</v>
@@ -1922,7 +1920,7 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B25">
         <v>20</v>
@@ -1931,10 +1929,10 @@
         <v>10</v>
       </c>
       <c r="E25" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G25" t="s">
         <v>10</v>
@@ -1958,10 +1956,10 @@
         <v>8</v>
       </c>
       <c r="N25" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="O25" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="P25" t="s">
         <v>11</v>
@@ -1969,7 +1967,7 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B26">
         <v>20</v>
@@ -1978,10 +1976,10 @@
         <v>20</v>
       </c>
       <c r="E26" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G26" t="s">
         <v>10</v>
@@ -2005,10 +2003,10 @@
         <v>8</v>
       </c>
       <c r="N26" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="O26" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="P26" t="s">
         <v>11</v>
@@ -2016,7 +2014,7 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -2028,10 +2026,10 @@
         <v>5</v>
       </c>
       <c r="E27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F27" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G27" t="s">
         <v>13</v>
@@ -2066,7 +2064,7 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28">
         <v>10</v>
@@ -2075,10 +2073,10 @@
         <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G28" t="s">
         <v>13</v>
@@ -2113,7 +2111,7 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -2122,10 +2120,10 @@
         <v>10</v>
       </c>
       <c r="E29" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G29" t="s">
         <v>13</v>
@@ -2160,7 +2158,7 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30">
         <v>10</v>
@@ -2169,10 +2167,10 @@
         <v>10</v>
       </c>
       <c r="E30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
@@ -2207,7 +2205,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -2216,10 +2214,10 @@
         <v>20</v>
       </c>
       <c r="E31" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F31" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
@@ -2254,7 +2252,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B32">
         <v>10</v>
@@ -2263,10 +2261,10 @@
         <v>20</v>
       </c>
       <c r="E32" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
@@ -2301,7 +2299,7 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -2310,10 +2308,10 @@
         <v>30</v>
       </c>
       <c r="E33" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F33" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G33" t="s">
         <v>13</v>
@@ -2348,7 +2346,7 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B34">
         <v>10</v>
@@ -2357,10 +2355,10 @@
         <v>30</v>
       </c>
       <c r="E34" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F34" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G34" t="s">
         <v>13</v>
@@ -2395,7 +2393,7 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -2407,10 +2405,10 @@
         <v>5</v>
       </c>
       <c r="E35" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G35" t="s">
         <v>13</v>
@@ -2445,7 +2443,7 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B36">
         <v>10</v>
@@ -2454,10 +2452,10 @@
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G36" t="s">
         <v>13</v>
@@ -2492,7 +2490,7 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B37">
         <v>20</v>
@@ -2501,10 +2499,10 @@
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G37" t="s">
         <v>13</v>
@@ -2539,7 +2537,7 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38">
         <v>30</v>
@@ -2548,10 +2546,10 @@
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G38" t="s">
         <v>13</v>
@@ -2586,7 +2584,7 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -2595,10 +2593,10 @@
         <v>10</v>
       </c>
       <c r="E39" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F39" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G39" t="s">
         <v>13</v>
@@ -2633,7 +2631,7 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40">
         <v>10</v>
@@ -2642,10 +2640,10 @@
         <v>10</v>
       </c>
       <c r="E40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G40" t="s">
         <v>13</v>
@@ -2680,7 +2678,7 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41">
         <v>20</v>
@@ -2689,10 +2687,10 @@
         <v>10</v>
       </c>
       <c r="E41" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G41" t="s">
         <v>13</v>
@@ -2727,7 +2725,7 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B42">
         <v>30</v>
@@ -2736,10 +2734,10 @@
         <v>10</v>
       </c>
       <c r="E42" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F42" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G42" t="s">
         <v>13</v>
@@ -2774,7 +2772,7 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B43">
         <v>60</v>
@@ -2786,13 +2784,13 @@
         <v>70</v>
       </c>
       <c r="E43" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="F43" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H43">
         <v>0.4</v>
@@ -2819,12 +2817,12 @@
         <v>14</v>
       </c>
       <c r="P43" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B44">
         <v>60</v>
@@ -2836,13 +2834,13 @@
         <v>50</v>
       </c>
       <c r="E44" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="F44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G44" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H44">
         <v>0.4</v>
@@ -2869,12 +2867,12 @@
         <v>14</v>
       </c>
       <c r="P44" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B45">
         <v>50</v>
@@ -2886,13 +2884,13 @@
         <v>70</v>
       </c>
       <c r="E45" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="F45" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G45" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H45">
         <v>0.2</v>
@@ -2919,12 +2917,12 @@
         <v>14</v>
       </c>
       <c r="P45" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B46">
         <v>50</v>
@@ -2936,13 +2934,13 @@
         <v>50</v>
       </c>
       <c r="E46" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="F46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G46" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H46">
         <v>0.2</v>
@@ -2969,7 +2967,7 @@
         <v>14</v>
       </c>
       <c r="P46" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.3">
@@ -2986,7 +2984,7 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="F47" t="s">
         <v>16</v>
@@ -3013,13 +3011,13 @@
         <v>8</v>
       </c>
       <c r="N47" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="O47" t="s">
+        <v>93</v>
+      </c>
+      <c r="P47" t="s">
         <v>18</v>
-      </c>
-      <c r="P47" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.3">
@@ -3036,7 +3034,7 @@
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="F48" t="s">
         <v>16</v>
@@ -3063,18 +3061,18 @@
         <v>8</v>
       </c>
       <c r="N48" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="O48" t="s">
+        <v>93</v>
+      </c>
+      <c r="P48" t="s">
         <v>18</v>
-      </c>
-      <c r="P48" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B49">
         <v>100</v>
@@ -3086,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="F49" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G49" t="s">
         <v>17</v>
@@ -3113,13 +3111,13 @@
         <v>8</v>
       </c>
       <c r="N49" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="O49" t="s">
+        <v>93</v>
+      </c>
+      <c r="P49" t="s">
         <v>18</v>
-      </c>
-      <c r="P49" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
